--- a/docs/jp/04_要件定義書.xlsx
+++ b/docs/jp/04_要件定義書.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>初版受信者納品候補確定. 全合格判定基準充足: 引用源 8 件全件実在 / 形式 100% 準拠 / 独立確認担当 round 2 PASS 無条件 / 用語規律監査 round 1 指摘実体修正済 / 用户口頭承認 (2026-04-29).</t>
+          <t>初版受信者納品候補確定. 全合格判定基準充足: 引用源 8 件全件実在 / 形式 100% 準拠 / 独立確認担当 第 2 回 無条件合格 / 用語規律監査 第 1 回 指摘実体修正済 / 用户口頭承認 (2026-04-29).</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
